--- a/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
+++ b/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
@@ -1,122 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\test\cims-models\csv\policies\reference\Ref_carbon tax\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF92A9F5-2B55-4EF8-A412-4BD82619D995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D02737F2-6751-4E37-A77E-2D653813B84E}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
-  <si>
-    <t>&lt;-- Navigate by typing to search</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>Sub_Context</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.BC</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>Combustion</t>
-  </si>
-  <si>
-    <t>$/tCO2e</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,35 +49,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="Control"/>
       <sheetName val="Macro"/>
       <sheetName val="Prices"/>
       <sheetName val="Carbon_tax"/>
       <sheetName val="Demand"/>
+      <sheetName val="Elec markups"/>
+      <sheetName val="CER"/>
       <sheetName val="Conversions"/>
       <sheetName val="Coefficients"/>
+      <sheetName val="macro inputs"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -200,6 +176,9 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -521,151 +500,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9BF1A2D-FE08-4724-BBBD-82296DA69DF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>&lt;-- Navigate by typing to search</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sub_Context</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>2000</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>2005</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>2010</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>2015</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>2020</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>2025</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>2030</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>2035</v>
       </c>
-      <c r="U2">
+      <c r="U2" t="n">
         <v>2040</v>
       </c>
-      <c r="V2">
+      <c r="V2" t="n">
         <v>2045</v>
       </c>
-      <c r="W2">
+      <c r="W2" t="n">
         <v>2050</v>
       </c>
-      <c r="X2" t="s">
-        <v>13</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.BC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M3">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N3">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>26.526018458051627</v>
-      </c>
-      <c r="P3">
-        <v>33.304393348006798</v>
-      </c>
-      <c r="Q3">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v>26.52601845805163</v>
+      </c>
+      <c r="P3" t="n">
+        <v>33.3043933480068</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45</v>
       </c>
       <c r="R3">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S3">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T3">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U3">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V3">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W3">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
+++ b/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -501,12 +501,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
+++ b/csv/policies/reference/Ref_carbon tax/formula_Ref_carbon tax_BC.xlsx
@@ -1,36 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\test\cims-models\csv\policies\reference\Ref_carbon tax\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813343E4-DA78-46A5-90AA-193E815CFD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
+  <calcPr calcId="191029" iterate="1" calcOnSave="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+  <si>
+    <t>&lt;-- Navigate by typing to search</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>Sub_Context</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>CIMS.CAN.BC</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>tax</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>Combustion</t>
+  </si>
+  <si>
+    <t>$/tCO2e</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,86 +154,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Control"/>
       <sheetName val="Macro"/>
@@ -137,48 +186,672 @@
       <sheetName val="Demand"/>
       <sheetName val="Elec markups"/>
       <sheetName val="CER"/>
+      <sheetName val="AFDC"/>
       <sheetName val="Conversions"/>
       <sheetName val="Coefficients"/>
-      <sheetName val="macro inputs"/>
     </sheetNames>
+    <definedNames>
+      <definedName name="region_CIMS" refersTo="='Control'!$B$19:$B$34"/>
+    </definedNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="0">
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>CAN</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>BC</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>AB</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>SK</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>MB</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>ON</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>QC</v>
+          </cell>
+        </row>
         <row r="26">
-          <cell r="K26">
-            <v>0</v>
-          </cell>
-          <cell r="L26">
-            <v>0</v>
-          </cell>
-          <cell r="P26">
-            <v>68.341643330825832</v>
-          </cell>
-          <cell r="Q26">
+          <cell r="B26" t="str">
+            <v>NB</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>NS</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>PE</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>NL</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>YT</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>NT</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>NU</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>AT</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>TR</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Population forecast</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="4">
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>30</v>
+          </cell>
+          <cell r="Q4">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R4">
             <v>100.32134973994673</v>
           </cell>
-          <cell r="R26">
-            <v>82.639006798408047</v>
-          </cell>
-          <cell r="S26">
-            <v>67.75892127087694</v>
-          </cell>
-          <cell r="T26">
-            <v>55.57940835560332</v>
-          </cell>
-          <cell r="U26">
+          <cell r="S4">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T4">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U4">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V4">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>26.526018458051627</v>
+          </cell>
+          <cell r="O5">
+            <v>33.304393348006798</v>
+          </cell>
+          <cell r="P5">
+            <v>40</v>
+          </cell>
+          <cell r="Q5">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R5">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S5">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T5">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U5">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V5">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>30</v>
+          </cell>
+          <cell r="Q6">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R6">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S6">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T6">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U6">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V6">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>0</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>30</v>
+          </cell>
+          <cell r="Q7">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R7">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S7">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T7">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U7">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V7">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8">
+            <v>0</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>30</v>
+          </cell>
+          <cell r="Q8">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R8">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S8">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T8">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U8">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V8">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9">
+            <v>0</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>30</v>
+          </cell>
+          <cell r="Q9">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R9">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S9">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T9">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U9">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V9">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>18.87248956387052</v>
+          </cell>
+          <cell r="P10">
+            <v>22.15</v>
+          </cell>
+          <cell r="Q10">
+            <v>28.660327055790539</v>
+          </cell>
+          <cell r="R10">
+            <v>42.071606038310293</v>
+          </cell>
+          <cell r="S10">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T10">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U10">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V10">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>30</v>
+          </cell>
+          <cell r="Q11">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R11">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S11">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T11">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U11">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V11">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>30</v>
+          </cell>
+          <cell r="Q12">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R12">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S12">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T12">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U12">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V12">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>30</v>
+          </cell>
+          <cell r="Q13">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R13">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S13">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T13">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U13">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V13">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>30</v>
+          </cell>
+          <cell r="Q14">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R14">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S14">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T14">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U14">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V14">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>30</v>
+          </cell>
+          <cell r="Q15">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R15">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S15">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T15">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U15">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V15">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>30</v>
+          </cell>
+          <cell r="Q16">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R16">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S16">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T16">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U16">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V16">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>30</v>
+          </cell>
+          <cell r="Q17">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R17">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S17">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T17">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U17">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V17">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="L18">
+            <v>0</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="P18">
+            <v>30</v>
+          </cell>
+          <cell r="Q18">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R18">
+            <v>100.32134973994673</v>
+          </cell>
+          <cell r="S18">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T18">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U18">
+            <v>55.57940835560332</v>
+          </cell>
+          <cell r="V18">
+            <v>45.789061745779293</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>30</v>
+          </cell>
+          <cell r="Q19">
+            <v>68.341643330825832</v>
+          </cell>
+          <cell r="R19">
+            <v>100.32134973994671</v>
+          </cell>
+          <cell r="S19">
+            <v>82.639006798408047</v>
+          </cell>
+          <cell r="T19">
+            <v>67.75892127087694</v>
+          </cell>
+          <cell r="U19">
+            <v>55.579408355603313</v>
+          </cell>
+          <cell r="V19">
             <v>45.789061745779293</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -500,197 +1173,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:X3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>&lt;-- Navigate by typing to search</t>
-        </is>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sub_Context</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2">
         <v>2000</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>2005</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>2010</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>2015</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>2020</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>2025</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>2030</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>2035</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>2040</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>2045</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2">
         <v>2050</v>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
+      <c r="X2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIMS.CAN.BC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>tax</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CO2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Combustion</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>$/tCO2e</t>
-        </is>
-      </c>
-      <c r="M3">
-        <f>[1]Prices!K$26</f>
-        <v/>
-      </c>
-      <c r="N3">
-        <f>[1]Prices!L$26</f>
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v>26.52601845805163</v>
-      </c>
-      <c r="P3" t="n">
-        <v>33.3043933480068</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>45</v>
-      </c>
-      <c r="R3">
-        <f>[1]Prices!P$26</f>
-        <v/>
-      </c>
-      <c r="S3">
-        <f>[1]Prices!Q$26</f>
-        <v/>
-      </c>
-      <c r="T3">
-        <f>[1]Prices!R$26</f>
-        <v/>
-      </c>
-      <c r="U3">
-        <f>[1]Prices!S$26</f>
-        <v/>
-      </c>
-      <c r="V3">
-        <f>[1]Prices!T$26</f>
-        <v/>
-      </c>
-      <c r="W3">
-        <f>[1]Prices!U$26</f>
-        <v/>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" cm="1">
+        <f t="array" ref="M3">INDEX([1]Carbon_tax!L$4:L$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>0</v>
+      </c>
+      <c r="N3" cm="1">
+        <f t="array" ref="N3">INDEX([1]Carbon_tax!M$4:M$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>0</v>
+      </c>
+      <c r="O3" cm="1">
+        <f t="array" ref="O3">INDEX([1]Carbon_tax!N$4:N$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>26.526018458051627</v>
+      </c>
+      <c r="P3" cm="1">
+        <f t="array" ref="P3">INDEX([1]Carbon_tax!O$4:O$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>33.304393348006798</v>
+      </c>
+      <c r="Q3" cm="1">
+        <f t="array" ref="Q3">INDEX([1]Carbon_tax!P$4:P$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>40</v>
+      </c>
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">INDEX([1]Carbon_tax!Q$4:Q$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>68.341643330825832</v>
+      </c>
+      <c r="S3" cm="1">
+        <f t="array" ref="S3">INDEX([1]Carbon_tax!R$4:R$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>100.32134973994673</v>
+      </c>
+      <c r="T3" cm="1">
+        <f t="array" ref="T3">INDEX([1]Carbon_tax!S$4:S$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>82.639006798408047</v>
+      </c>
+      <c r="U3" cm="1">
+        <f t="array" ref="U3">INDEX([1]Carbon_tax!T$4:T$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>67.75892127087694</v>
+      </c>
+      <c r="V3" cm="1">
+        <f t="array" ref="V3">INDEX([1]Carbon_tax!U$4:U$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>55.57940835560332</v>
+      </c>
+      <c r="W3" cm="1">
+        <f t="array" ref="W3">INDEX([1]Carbon_tax!V$4:V$19,_xlfn.XMATCH($C3,[1]!region_CIMS))</f>
+        <v>45.789061745779293</v>
       </c>
     </row>
   </sheetData>
